--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/getAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/getAdmin-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
-  <si>
-    <t>Statement: UserService.getAdmin(adminId) – Delegates to userRepository.findAdminById(). Propagates NotFoundError if absent.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
+  <si>
+    <t>Statement: UserService.getAdmin(adminId)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: adminId: string</t>
+    <t>Input: adminId</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository is accessible</t>
+    <t>userRepository accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;AdminWithUser&gt;  OR  throws NotFoundError</t>
+    <t>Output: Promise&lt;AdminWithUser&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: AdminWithUser returned. On NotFoundError: no state change.</t>
+    <t>Admin returned.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,15 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>admin existence</t>
-  </si>
-  <si>
-    <t>admin with given adminId exists</t>
-  </si>
-  <si>
-    <t>no admin (NotFoundError)</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -88,36 +79,12 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>adminId="admin-001" (existing)</t>
-  </si>
-  <si>
-    <t>Returns AdminWithUser; findAdminById called with id</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>"nonexistent-id"</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>ID is opaque string</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
@@ -127,19 +94,13 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Existing adminId</t>
-  </si>
-  <si>
-    <t>Returns AdminWithUser</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Non-existent id</t>
+    <t>Get admin</t>
+  </si>
+  <si>
+    <t>Success/Error</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -697,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -719,34 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -755,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -767,53 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -834,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -874,19 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -910,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -933,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -953,19 +841,79 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -993,16 +941,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1010,45 +958,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1057,19 +1005,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/getAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/getAdmin-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
-  <si>
-    <t>Statement: UserService.getAdmin(adminId)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
+  <si>
+    <t>Statement: UserService.getAdmin(adminId) – Retrieves an admin by ID. Returns AdminWithUser on success. Throws NotFoundError if no admin exists with the given ID.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: adminId</t>
+    <t>Input: adminId: string</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository accessible</t>
+    <t>An admin with the given ID may or may not exist in the system.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Admin returned.</t>
+    <t>On success: AdminWithUser returned matching the given ID. On failure: NotFoundError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,15 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Admin existence</t>
+  </si>
+  <si>
+    <t>Existing ID → AdminWithUser returned</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,28 +88,67 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: valid UUID (existing admin)</t>
+  </si>
+  <si>
+    <t>Full AdminWithUser object returned</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>id: valid UUID (no match)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Admin not found")</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ""</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match)</t>
+  </si>
+  <si>
+    <t>id: "a" (found)</t>
+  </si>
+  <si>
+    <t>AdminWithUser returned with id: "a" and correct user data</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Get admin</t>
-  </si>
-  <si>
-    <t>Success/Error</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>BVA-1</t>
   </si>
   <si>
     <t>Testing</t>
@@ -133,7 +181,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>SERV-06</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +728,34 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +764,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +776,53 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +843,24 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +871,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +883,70 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>19</v>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -798,22 +970,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +993,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1013,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1033,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1053,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1073,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -941,16 +1113,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -958,39 +1130,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1">
         <v>5</v>
@@ -1005,19 +1177,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/getAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/getAdmin-bbt-form.xlsx
@@ -181,7 +181,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-06</t>
+    <t>SERV-07</t>
   </si>
   <si>
     <t>n/a</t>
